--- a/Config/Datas/Tables/s_刷新阶段_SpawnPhaseConfig.xlsx
+++ b/Config/Datas/Tables/s_刷新阶段_SpawnPhaseConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSpawnPhase" sheetId="1" r:id="R7c8d6e7e3fa5434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbSpawnPhase" sheetId="1" r:id="R1a6ac1d25c5c4a76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -481,7 +481,7 @@
         <x:v>4250</x:v>
       </x:c>
       <x:c r="H6" s="5" t="str">
-        <x:v>10010:35;10011:20;10012:25;10013:20</x:v>
+        <x:v>10010:25;10011:10;10012:15;10013:10;10014:15;10015:10;10016:10;10017:5</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -505,7 +505,7 @@
         <x:v>2800</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str">
-        <x:v>10010:25;10011:25;10012:25;10013:25</x:v>
+        <x:v>10010:15;10011:10;10012:10;10013:15;10014:10;10015:15;10016:15;10017:10</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -529,7 +529,76 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="H8" s="5" t="str">
-        <x:v>10010:20;10011:30;10012:20;10013:30</x:v>
+        <x:v>10010:10;10011:10;10012:10;10013:15;10014:10;10015:15;10016:15;10017:15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="B9" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>4400</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>10010:70;10012:30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="B10" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>4100</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>10010:30;10011:20;10012:25;10014:25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="B11" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>240000</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>3800</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>10011:25;10013:25;10014:25;10017:25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
